--- a/data_output/manuscript_tables.xlsx
+++ b/data_output/manuscript_tables.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="173">
   <si>
-    <t xml:space="preserve">Manuscript tables -- exported from probabilistic_risk_characterization.qmd, rendered 2026-08-26</t>
+    <t xml:space="preserve">Manuscript tables -- exported from probabilistic_risk_characterization.qmd, rendered 2026-08-29</t>
   </si>
   <si>
     <t xml:space="preserve">Sheet</t>
